--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-medicationstatement.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-medicationstatement.xlsx
@@ -293,7 +293,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -719,10 +719,10 @@
 </t>
   </si>
   <si>
-    <t>薬物測定に関連する遭遇 /エピソード / Encounter / Episode associated with MedicationStatement</t>
-  </si>
-  <si>
-    <t>この薬物測定のコンテキストを確立する遭遇またはケアのエピソード。 / The encounter or episode of care that establishes the context for this MedicationStatement.</t>
+    <t>薬物測定に関連するEnounter /エピソード / Encounter / Episode associated with MedicationStatement</t>
+  </si>
+  <si>
+    <t>この薬物測定のコンテキストを確立するEnounterまたはケアのエピソード。 / The encounter or episode of care that establishes the context for this MedicationStatement.</t>
   </si>
   <si>
     <t>Event.context</t>

--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-medicationstatement.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-medicationstatement.xlsx
@@ -388,7 +388,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -519,7 +519,7 @@
     <t>MedicationStatement.basedOn</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest|CarePlan|ServiceRequest)
+    <t xml:space="preserve">Reference(MedicationRequest|4.0.1|CarePlan|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -541,7 +541,7 @@
     <t>MedicationStatement.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Observation)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Observation|4.0.1)
 </t>
   </si>
   <si>
@@ -563,7 +563,7 @@
     <t>MedicationStatement.status</t>
   </si>
   <si>
-    <t>アクティブ|完了|エラーに入った|意図した|停止|オンホールド|不明|非テイク / active | completed | entered-in-error | intended | stopped | on-hold | unknown | not-taken</t>
+    <t>アクティブ | 完了 | エラー入力 | 意図的 | 停止 | 保留 | 不明 | 未取得 / active | completed | entered-in-error | intended | stopped | on-hold | unknown | not-taken</t>
   </si>
   <si>
     <t>服薬状況のを示す。コード表： http://hl7.org/fhir/CodeSystem/medication-statement-status
@@ -613,7 +613,7 @@
     <t>ステートメントのステータスの理由を示すコード化された概念。 / A coded concept indicating the reason for the status of the statement.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/reason-medication-status-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/reason-medication-status-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -637,7 +637,7 @@
     <t>薬剤が含まれている場所を識別するコード化された概念は、薬物測定に含まれる場所が消費または投与されると予想されます。 / A coded concept identifying where the medication included in the MedicationStatement is expected to be consumed or administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-statement-category</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-statement-category|4.0.1</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication usage"].value</t>
@@ -715,7 +715,7 @@
     <t>MedicationStatement.context</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|EpisodeOfCare)
+    <t xml:space="preserve">Reference(Encounter|4.0.1|EpisodeOfCare|4.0.1)
 </t>
   </si>
   <si>
@@ -897,7 +897,7 @@
     <t>MedicationStatement.informationSource</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Practitioner|PractitionerRole|RelatedPerson|Organization)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -913,7 +913,7 @@
     <t>MedicationStatement.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -944,7 +944,7 @@
     <t>薬が服用されている理由を特定するコード化された概念。 / A coded concept identifying why the medication is being taken.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-code|4.0.1</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1017,7 +1017,7 @@
     <t>MedicationStatement.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Observation|DiagnosticReport)
+    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1)
 </t>
   </si>
   <si>
@@ -1380,17 +1380,17 @@
   <dimension ref="A1:AN36"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="55.7578125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="41.7890625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="14.8203125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="47.8046875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="35.828125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="12.70703125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="96.375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="105.265625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1399,26 +1399,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="188.5859375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="58.140625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="38.25" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="161.6796875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.28125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="32.79296875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="140.73046875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="45.6171875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="120.65234375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="39.109375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-medicationstatement.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-medicationstatement.xlsx
@@ -93,7 +93,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
